--- a/output/pdf_financials_xlsx/CACR.xlsx
+++ b/output/pdf_financials_xlsx/CACR.xlsx
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>33.035</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -5632,7 +5632,11 @@
           <t>Secured convertible promissory note issued for exploration and evaluation expenditures 13</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>33</v>
       </c>
@@ -5668,7 +5672,11 @@
           <t>Shares issued for exploration and evaluation expenditures 15</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.035</v>
       </c>

--- a/output/pdf_financials_xlsx/CACR.xlsx
+++ b/output/pdf_financials_xlsx/CACR.xlsx
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.9216800000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.310473</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.081037</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.674027</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.9216800000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.310473</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.081037</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.674027</v>
       </c>
     </row>
     <row r="37">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.936598</v>
+        <v>0.014918</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.354777</v>
+        <v>0.044304</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.087602</v>
+        <v>0.006565</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.738973</v>
+        <v>0.064946</v>
       </c>
     </row>
     <row r="49">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">

--- a/output/pdf_financials_xlsx/CACR.xlsx
+++ b/output/pdf_financials_xlsx/CACR.xlsx
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3.206311</v>
+        <v>-3.206311</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.144</v>
+        <v>-0.144</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1509,16 +1509,16 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>0</v>
+        <v>0.056223</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>0</v>
+        <v>0.060948</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>0</v>
+        <v>0.086689</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0</v>
+        <v>0.086689</v>
       </c>
     </row>
     <row r="57">
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>0</v>
+        <v>0.021865</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>0</v>
+        <v>0.041393</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>0</v>
+        <v>0.067166</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0</v>
+        <v>0.077321</v>
       </c>
     </row>
     <row r="58">
@@ -1661,16 +1661,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.162094</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.543014</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.748898</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>1.081709</v>
       </c>
     </row>
     <row r="65">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>3.383171</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>3.969677</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>4.49384</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>4.736678</v>
       </c>
     </row>
     <row r="68">
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>3.545265</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>4.512691</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>5.242738</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>5.818387</v>
       </c>
     </row>
     <row r="69">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>4.376717</v>
+        <v>0.831452</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>5.441049</v>
+        <v>0.928358</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>6.335605</v>
+        <v>1.092867</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>39.947018</v>
+        <v>34.128631</v>
       </c>
     </row>
     <row r="76">
@@ -2523,16 +2523,16 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.826604</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>2.479213</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>3.156816</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>3.739542</v>
       </c>
     </row>
     <row r="111">
@@ -4374,7 +4374,11 @@
           <t>Accretion expense 12,13,14</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>0.826604</v>
       </c>
@@ -4574,7 +4578,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -5960,7 +5968,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>-3.206311</v>
       </c>
@@ -6712,7 +6724,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>3.206311</v>
       </c>
